--- a/dataset_statistics.xlsx
+++ b/dataset_statistics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johannes/Documents/GitHub/differentiable-er/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F86F11E-2CD8-D146-B8DD-47D87D495DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA4E7342-BA72-2B4E-96F7-7E39E802E2EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18220" yWindow="8700" windowWidth="28040" windowHeight="17440" xr2:uid="{AA86EB36-6225-4D46-9F29-36447E715E62}"/>
+    <workbookView xWindow="29120" yWindow="13460" windowWidth="28040" windowHeight="17440" xr2:uid="{AA86EB36-6225-4D46-9F29-36447E715E62}"/>
   </bookViews>
   <sheets>
     <sheet name="dataset_statistics" sheetId="1" r:id="rId1"/>
@@ -71,6 +71,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -597,7 +600,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -640,32 +643,35 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="11" xfId="42" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="16" xfId="42" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -693,6 +699,7 @@
     <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="42" builtinId="3"/>
     <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
     <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
@@ -1042,306 +1049,307 @@
   <dimension ref="B1:H14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="21.5" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
     <col min="8" max="8" width="17.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="9">
         <v>24</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="9">
         <v>20.04</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="9">
         <v>11</v>
       </c>
       <c r="G3" s="14">
         <v>13087</v>
       </c>
-      <c r="H3" s="15">
+      <c r="H3" s="10">
         <v>175</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="7"/>
-      <c r="C4" s="12" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="4">
         <v>26</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="4">
         <v>12.86</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="4">
         <v>8</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="15">
         <v>12595</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="5">
         <v>35</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="9">
         <v>26</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="9">
         <v>38.159999999999997</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="9">
         <v>35</v>
       </c>
       <c r="G5" s="14">
         <v>31509</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="10">
         <v>180</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="7"/>
-      <c r="C6" s="12" t="s">
+      <c r="B6" s="12"/>
+      <c r="C6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="4">
         <v>28</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="4">
         <v>24.99</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="4">
         <v>23</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="15">
         <v>30189</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="5">
         <v>41</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="9">
         <v>42</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="9">
         <v>6.34</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="9">
         <v>5</v>
       </c>
       <c r="G7" s="14">
         <v>251734</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="10">
         <v>990</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="7"/>
-      <c r="C8" s="12" t="s">
+      <c r="B8" s="12"/>
+      <c r="C8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="4">
         <v>38</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="4">
         <v>7.1</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="4">
         <v>7</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="15">
         <v>239734</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="5">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="9">
         <v>29</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="9">
         <v>8.69</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="9">
         <v>8</v>
       </c>
       <c r="G9" s="14">
         <v>2099</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="10">
         <v>21</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="7"/>
-      <c r="C10" s="12" t="s">
+      <c r="B10" s="12"/>
+      <c r="C10" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="4">
         <v>31</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="4">
         <v>10.48</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="4">
         <v>10</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="15">
         <v>2030</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="5">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="9">
         <v>19</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="9">
         <v>5.34</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="9">
         <v>5</v>
       </c>
       <c r="G11" s="14">
         <v>6886</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="10">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="7"/>
-      <c r="C12" s="12" t="s">
+      <c r="B12" s="12"/>
+      <c r="C12" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="4">
         <v>20</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="4">
         <v>7.13</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="4">
         <v>7</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="15">
         <v>6579</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="5">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13">
         <v>51</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13">
         <v>12.25</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13">
         <v>11</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="16">
         <v>7065</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="3">
         <v>90</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="7"/>
-      <c r="C14" s="12" t="s">
+      <c r="B14" s="12"/>
+      <c r="C14" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="4">
         <v>53</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="4">
         <v>13.21</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="4">
         <v>12</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="15">
         <v>6714</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="5">
         <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B13:B14"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="B13:B14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
